--- a/courses.xlsx
+++ b/courses.xlsx
@@ -425,23 +425,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Course code</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Course name</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Programming 101</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Mon-Wed</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>08:00-10:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dr. Ahmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Data Structures</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sun-Tue</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10:00-12:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dr. Sarah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Database Systems</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mon-Wed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13:00-15:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dr. Khalid</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>08:00-11:00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dr. Reem</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sun-Tue</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13:00-15:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dr. Fahad</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Calculus I</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sun-Tue-Thu</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>08:00-09:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dr. Omar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Physics II</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mon-Wed</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10:00-12:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dr. Yasser</t>
         </is>
       </c>
     </row>
